--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -18,13 +18,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="basefont"/>
+      <sz val="9.0"/>
+      <color rgb="002D3C51"/>
+      <u val="none"/>
     </font>
     <font>
       <name val="basefont"/>
@@ -264,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
@@ -282,6 +288,9 @@
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -400,7 +409,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -440,7 +449,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M2" s="6"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
@@ -463,7 +476,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -503,7 +516,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M3" s="6"/>
+      <c r="M3" s="7"/>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
@@ -526,7 +539,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -566,7 +579,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -593,7 +606,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -633,7 +646,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="7"/>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
@@ -656,7 +669,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -696,7 +709,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M6" s="6"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
@@ -719,7 +732,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -759,7 +772,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M7" s="6"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -782,7 +795,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -822,7 +835,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M8" s="6"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -845,7 +858,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -885,7 +898,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M9" s="6"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -908,7 +921,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -948,7 +961,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M10" s="6"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -971,7 +984,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1011,7 +1024,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M11" s="6"/>
+      <c r="M11" s="7"/>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
@@ -1034,7 +1047,7 @@
           <t>임상병리학과</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>바이오헬스맞춤형정밀진단전문가과정(소단위_주문식)</t>
         </is>
@@ -1074,7 +1087,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M12" s="6"/>
+      <c r="M12" s="7"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -1097,7 +1110,7 @@
           <t>방사선학과</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1137,7 +1150,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M13" s="6"/>
+      <c r="M13" s="7"/>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
@@ -1160,7 +1173,7 @@
           <t>방사선학과</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1200,7 +1213,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1227,7 +1240,7 @@
           <t>방사선학과</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1267,7 +1280,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M15" s="6"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
@@ -1290,7 +1303,7 @@
           <t>방사선학과</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1330,7 +1343,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M16" s="6"/>
+      <c r="M16" s="7"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
@@ -1353,7 +1366,7 @@
           <t>방사선학과</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1393,7 +1406,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M17" s="6"/>
+      <c r="M17" s="7"/>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
@@ -1416,7 +1429,7 @@
           <t>방사선학과</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1456,7 +1469,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1483,7 +1496,7 @@
           <t>방사선학과</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1523,7 +1536,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M19" s="6"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
@@ -1546,7 +1563,7 @@
           <t>방사선학과</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1586,7 +1603,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1613,7 +1630,7 @@
           <t>치기공학과</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1653,7 +1670,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M21" s="6"/>
+      <c r="M21" s="7"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
@@ -1676,7 +1693,7 @@
           <t>치기공학과</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1716,7 +1733,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M22" s="6"/>
+      <c r="M22" s="7"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -1739,7 +1756,7 @@
           <t>치기공학과</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1779,7 +1796,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M23" s="6"/>
+      <c r="M23" s="7"/>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
@@ -1802,7 +1819,7 @@
           <t>치기공학과</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1842,7 +1859,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M24" s="6"/>
+      <c r="M24" s="7"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
@@ -1865,7 +1882,7 @@
           <t>치기공학과</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1905,7 +1922,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M25" s="6"/>
+      <c r="M25" s="7"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
@@ -1928,7 +1945,7 @@
           <t>치기공학과</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -1968,7 +1985,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M26" s="6"/>
+      <c r="M26" s="7"/>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
@@ -1991,7 +2008,7 @@
           <t>치기공학과</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2031,7 +2048,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M27" s="6"/>
+      <c r="M27" s="7"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -2054,7 +2071,7 @@
           <t>치기공학과</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2094,7 +2111,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M28" s="6"/>
+      <c r="M28" s="7"/>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
@@ -2117,7 +2134,7 @@
           <t>치위생학과</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2157,7 +2174,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M29" s="6"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
@@ -2180,7 +2197,7 @@
           <t>치위생학과</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2220,7 +2237,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M30" s="6"/>
+      <c r="M30" s="7"/>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
@@ -2243,7 +2260,7 @@
           <t>치위생학과</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2283,7 +2300,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2310,7 +2327,7 @@
           <t>치위생학과</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2350,7 +2367,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M32" s="6"/>
+      <c r="M32" s="7"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
@@ -2373,7 +2390,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2413,7 +2430,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M33" s="6"/>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
@@ -2436,7 +2457,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2476,7 +2497,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M34" s="6"/>
+      <c r="M34" s="7"/>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
@@ -2499,7 +2520,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2539,7 +2560,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M35" s="6"/>
+      <c r="M35" s="7"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
@@ -2562,7 +2583,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2602,7 +2623,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M36" s="6"/>
+      <c r="M36" s="7"/>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
@@ -2625,7 +2646,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2665,7 +2686,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M37" s="6"/>
+      <c r="M37" s="7"/>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
@@ -2688,7 +2709,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2728,7 +2749,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M38" s="6"/>
+      <c r="M38" s="7"/>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
@@ -2751,7 +2772,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2791,7 +2812,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M39" s="6"/>
+      <c r="M39" s="7"/>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
@@ -2814,7 +2835,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2854,7 +2875,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M40" s="6"/>
+      <c r="M40" s="7"/>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
@@ -2877,7 +2898,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2917,7 +2938,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M41" s="6"/>
+      <c r="M41" s="7"/>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
@@ -2940,7 +2961,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -2980,7 +3001,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M42" s="6"/>
+      <c r="M42" s="7"/>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
@@ -3003,7 +3024,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3043,7 +3064,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M43" s="6"/>
+      <c r="M43" s="7"/>
     </row>
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
@@ -3066,7 +3087,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3106,7 +3127,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M44" s="6"/>
+      <c r="M44" s="7"/>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
@@ -3129,7 +3150,7 @@
           <t>물리치료학과</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3169,7 +3190,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M45" s="6"/>
+      <c r="M45" s="7"/>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
@@ -3192,7 +3213,7 @@
           <t>보건행정학과</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3232,7 +3253,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M46" s="6"/>
+      <c r="M46" s="7"/>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
@@ -3255,7 +3276,7 @@
           <t>보건행정학과</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3295,7 +3316,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M47" s="6"/>
+      <c r="M47" s="7"/>
     </row>
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
@@ -3318,7 +3339,7 @@
           <t>보건행정학과</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3358,7 +3379,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M48" s="6"/>
+      <c r="M48" s="7"/>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
@@ -3381,7 +3402,7 @@
           <t>보건행정학과</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3421,7 +3442,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M49" s="6"/>
+      <c r="M49" s="7"/>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
@@ -3444,7 +3465,7 @@
           <t>안경광학과</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3484,7 +3505,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M50" s="6"/>
+      <c r="M50" s="7"/>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
@@ -3507,7 +3528,7 @@
           <t>안경광학과</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3547,7 +3568,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M51" s="6" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3574,7 +3595,7 @@
           <t>안경광학과</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3614,7 +3635,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M52" s="6"/>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
@@ -3637,7 +3662,7 @@
           <t>안경광학과</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3677,7 +3702,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M53" s="6"/>
+      <c r="M53" s="7"/>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
@@ -3700,7 +3725,7 @@
           <t>언어치료학과</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3740,7 +3765,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M54" s="6"/>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
@@ -3763,7 +3792,7 @@
           <t>언어치료학과</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3803,7 +3832,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M55" s="6"/>
+      <c r="M55" s="7"/>
     </row>
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
@@ -3826,7 +3855,7 @@
           <t>언어치료학과</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3866,7 +3895,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M56" s="6"/>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
@@ -3889,7 +3922,7 @@
           <t>언어치료학과</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3929,7 +3962,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M57" s="6"/>
+      <c r="M57" s="7"/>
     </row>
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
@@ -3952,7 +3985,7 @@
           <t>언어치료학과</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -3992,7 +4025,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M58" s="6"/>
+      <c r="M58" s="7"/>
     </row>
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
@@ -4015,7 +4048,7 @@
           <t>작업치료학과</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>작업중심보조공학전문가과정(소단위_주문식)</t>
         </is>
@@ -4055,7 +4088,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M59" s="6"/>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
@@ -4078,7 +4115,7 @@
           <t>작업치료학과</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>작업중심보조공학전문가과정(소단위_주문식)</t>
         </is>
@@ -4118,7 +4155,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M60" s="6"/>
+      <c r="M60" s="7"/>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
@@ -4141,7 +4178,7 @@
           <t>작업치료학과</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>작업중심보조공학전문가과정(소단위_주문식)</t>
         </is>
@@ -4181,7 +4218,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M61" s="6"/>
+      <c r="M61" s="7"/>
     </row>
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
@@ -4204,7 +4241,7 @@
           <t>작업치료학과</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>작업중심보조공학전문가과정(소단위_주문식)</t>
         </is>
@@ -4244,7 +4281,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M62" s="6"/>
+      <c r="M62" s="7"/>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
@@ -4267,7 +4304,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4307,7 +4344,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M63" s="6"/>
+      <c r="M63" s="7"/>
     </row>
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
@@ -4330,7 +4367,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4370,7 +4407,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M64" s="6"/>
+      <c r="M64" s="7"/>
     </row>
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
@@ -4393,7 +4430,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4433,7 +4470,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M65" s="6"/>
+      <c r="M65" s="7"/>
     </row>
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
@@ -4456,7 +4493,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4496,7 +4533,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M66" s="6"/>
+      <c r="M66" s="7"/>
     </row>
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
@@ -4519,7 +4556,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4559,7 +4596,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M67" s="6"/>
+      <c r="M67" s="7"/>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
@@ -4582,7 +4619,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4622,7 +4659,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M68" s="6"/>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
@@ -4645,7 +4686,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4685,7 +4726,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M69" s="6" t="inlineStr">
+      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4712,7 +4753,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4752,7 +4793,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M70" s="6"/>
+      <c r="M70" s="7"/>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
@@ -4775,7 +4816,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4815,7 +4856,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M71" s="6"/>
+      <c r="M71" s="7"/>
     </row>
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
@@ -4838,7 +4879,7 @@
           <t>뷰티코디네이션학과</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4878,7 +4919,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M72" s="6"/>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
@@ -4901,7 +4946,7 @@
           <t>유아교육학과</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -4941,7 +4986,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M73" s="6"/>
+      <c r="M73" s="7"/>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
@@ -4964,7 +5009,7 @@
           <t>유아교육학과</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5004,7 +5049,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M74" s="6"/>
+      <c r="M74" s="7"/>
     </row>
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
@@ -5027,7 +5072,7 @@
           <t>유아교육학과</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5067,7 +5112,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M75" s="6"/>
+      <c r="M75" s="7"/>
     </row>
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
@@ -5090,7 +5135,7 @@
           <t>유아교육학과</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5130,7 +5175,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M76" s="6"/>
+      <c r="M76" s="7"/>
     </row>
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
@@ -5153,7 +5198,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5193,7 +5238,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M77" s="6"/>
+      <c r="M77" s="7"/>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
@@ -5216,7 +5261,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5256,7 +5301,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M78" s="6"/>
+      <c r="M78" s="7"/>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
@@ -5279,7 +5324,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5319,7 +5364,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M79" s="6" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5346,7 +5391,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5386,7 +5431,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M80" s="6" t="inlineStr">
+      <c r="M80" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5413,7 +5458,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5453,7 +5498,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M81" s="6"/>
+      <c r="M81" s="7"/>
     </row>
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
@@ -5476,7 +5521,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5516,7 +5561,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M82" s="6"/>
+      <c r="M82" s="7"/>
     </row>
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
@@ -5539,7 +5584,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5579,7 +5624,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M83" s="6"/>
+      <c r="M83" s="7"/>
     </row>
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
@@ -5602,7 +5647,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5642,7 +5687,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M84" s="6"/>
+      <c r="M84" s="7"/>
     </row>
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
@@ -5665,7 +5710,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5705,7 +5750,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M85" s="6"/>
+      <c r="M85" s="7"/>
     </row>
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
@@ -5728,7 +5773,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5768,7 +5813,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M86" s="6"/>
+      <c r="M86" s="7"/>
     </row>
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
@@ -5791,7 +5836,7 @@
           <t>사회복지학과</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>학사학위 전공심화과정</t>
         </is>
@@ -5831,7 +5876,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M87" s="6"/>
+      <c r="M87" s="7"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -1343,7 +1343,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M16" s="7"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -2241,7 +2241,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M30" s="7"/>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
@@ -2690,7 +2694,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M37" s="7"/>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
@@ -4159,7 +4167,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M60" s="7"/>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
@@ -4285,7 +4297,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M62" s="7"/>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -5581,7 +5581,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M82" s="7"/>
+      <c r="M82" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
@@ -5770,7 +5774,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M85" s="7"/>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -2631,7 +2631,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M36" s="7"/>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
@@ -5258,7 +5262,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M77" s="7"/>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
@@ -5904,7 +5912,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M87" s="7"/>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -303,7 +303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.0" customWidth="true"/>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>작업치료학과</t>
+          <t>언어치료학과</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>작업중심보조공학전문가과정(소단위_주문식)</t>
+          <t>난독재활치료전문가양성과정(소단위_주문식)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -4076,27 +4076,27 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>880000000124</t>
+          <t>880000000080</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>700040</t>
+          <t>690057</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>운전재활,자동차보조공학</t>
+          <t>난독증진단평가</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>차선아</t>
+          <t>하지명</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -4143,17 +4143,17 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>880000000125</t>
+          <t>880000000124</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>700042</t>
+          <t>700040</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>인간공학</t>
+          <t>운전재활,자동차보조공학</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>강소라</t>
+          <t>차선아</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>880000000126</t>
+          <t>880000000125</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>700043</t>
+          <t>700042</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>임상작업치료학특론</t>
+          <t>인간공학</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>이정남</t>
+          <t>강소라</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -4238,7 +4238,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M61" s="7"/>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
@@ -4273,17 +4277,17 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>880000000127</t>
+          <t>880000000126</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>700052</t>
+          <t>700043</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>장애학</t>
+          <t>임상작업치료학특론</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -4293,7 +4297,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>김지훈</t>
+          <t>이정남</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -4301,11 +4305,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M62" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M62" s="7"/>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>뷰티코디네이션학과</t>
+          <t>작업치료학과</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>학사학위 전공심화과정</t>
+          <t>작업중심보조공학전문가과정(소단위_주문식)</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -4340,27 +4340,27 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>880000000059</t>
+          <t>880000000127</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>720001</t>
+          <t>700052</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>메디컬스킨케어실무</t>
+          <t>장애학</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>이지선</t>
+          <t>김지훈</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -4368,7 +4368,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M63" s="7"/>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
@@ -4403,17 +4407,17 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>880000000060</t>
+          <t>880000000059</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>720002</t>
+          <t>720001</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>모발미용학</t>
+          <t>메디컬스킨케어실무</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -4423,7 +4427,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>곽진만</t>
+          <t>이지선</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4466,17 +4470,17 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>880000000061</t>
+          <t>880000000060</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>720003</t>
+          <t>720002</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>뷰티퍼스널컬러&amp;코디</t>
+          <t>모발미용학</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -4486,7 +4490,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>이현주</t>
+          <t>곽진만</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -4529,17 +4533,17 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>880000000062</t>
+          <t>880000000061</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>720004</t>
+          <t>720003</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>살롱두피&amp;헤드스파</t>
+          <t>뷰티퍼스널컬러&amp;코디</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -4549,7 +4553,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>박정은</t>
+          <t>이현주</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4592,17 +4596,17 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>880000000063</t>
+          <t>880000000062</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>720005</t>
+          <t>720004</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>살롱미용영어</t>
+          <t>살롱두피&amp;헤드스파</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -4612,7 +4616,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>이상록</t>
+          <t>박정은</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4650,22 +4654,22 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>880000000064</t>
+          <t>880000000063</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>720011</t>
+          <t>720005</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>뷰티소셜미디어</t>
+          <t>살롱미용영어</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -4675,7 +4679,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>황예지</t>
+          <t>이상록</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4683,11 +4687,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M68" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M68" s="7"/>
     </row>
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
@@ -4722,17 +4722,17 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>880000000065</t>
+          <t>880000000064</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>720012</t>
+          <t>720011</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>살롱업스타일</t>
+          <t>뷰티소셜미디어</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>조미숙</t>
+          <t>황예지</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4789,17 +4789,17 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>880000000066</t>
+          <t>880000000065</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>720013</t>
+          <t>720012</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>스폐셜테라피</t>
+          <t>살롱업스타일</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>김명희</t>
+          <t>조미숙</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4817,7 +4817,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M70" s="7"/>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
@@ -4852,17 +4856,17 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>880000000067</t>
+          <t>880000000066</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>720014</t>
+          <t>720013</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>패션이미지메이크업&amp;스타일링</t>
+          <t>스폐셜테라피</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4872,7 +4876,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>홍주연</t>
+          <t>김명희</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4915,17 +4919,17 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>880000000068</t>
+          <t>880000000067</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>720015</t>
+          <t>720014</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>화장품트렌드분석</t>
+          <t>패션이미지메이크업&amp;스타일링</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -4935,7 +4939,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>김정은</t>
+          <t>홍주연</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4943,11 +4947,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M72" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M72" s="7"/>
     </row>
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>유아교육학과</t>
+          <t>뷰티코디네이션학과</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -4977,32 +4977,32 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>880000000097</t>
+          <t>880000000068</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>731039</t>
+          <t>720015</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>가족상담</t>
+          <t>화장품트렌드분석</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>최인영</t>
+          <t>김정은</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -5010,7 +5010,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M73" s="7"/>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
@@ -5045,17 +5049,17 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>880000000098</t>
+          <t>880000000097</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>731040</t>
+          <t>731039</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>장애영유아 통합교육</t>
+          <t>가족상담</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -5065,7 +5069,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>박정란</t>
+          <t>최인영</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -5108,17 +5112,17 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>880000000099</t>
+          <t>880000000098</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>731041</t>
+          <t>731040</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>장애유아 진단 평가</t>
+          <t>장애영유아 통합교육</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -5128,7 +5132,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>김혜정</t>
+          <t>박정란</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -5171,17 +5175,17 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>880000000100</t>
+          <t>880000000099</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>731042</t>
+          <t>731041</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>특수교구 및 교재개발</t>
+          <t>장애유아 진단 평가</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -5191,7 +5195,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>김영훈</t>
+          <t>김혜정</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -5219,7 +5223,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>사회복지학과</t>
+          <t>유아교육학과</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -5234,17 +5238,17 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>880000000101</t>
+          <t>880000000100</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>740037</t>
+          <t>731042</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>지역사회복지의 이해</t>
+          <t>특수교구 및 교재개발</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -5254,7 +5258,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>조재삼</t>
+          <t>김영훈</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -5262,11 +5266,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M77" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M77" s="7"/>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
@@ -5301,17 +5301,17 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>880000000102</t>
+          <t>880000000101</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>740040</t>
+          <t>740037</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>사회복지실천의 이해</t>
+          <t>지역사회복지의 이해</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>최은석</t>
+          <t>조재삼</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -5329,7 +5329,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M78" s="7"/>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
@@ -5364,17 +5368,17 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>880000000103</t>
+          <t>880000000102</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>740042</t>
+          <t>740040</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>인간행동의 이해</t>
+          <t>사회복지실천의 이해</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -5384,7 +5388,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>이재우</t>
+          <t>최은석</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -5392,11 +5396,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M79" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M79" s="7"/>
     </row>
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>880000000104</t>
+          <t>880000000103</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>740063</t>
+          <t>740042</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>사회복지지도감독론</t>
+          <t>인간행동의 이해</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>강상훈</t>
+          <t>이재우</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -5498,17 +5498,17 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>880000000105</t>
+          <t>880000000104</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>740065</t>
+          <t>740063</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>사회복지현장실무</t>
+          <t>사회복지지도감독론</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>김소영</t>
+          <t>강상훈</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -5526,7 +5526,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M81" s="7"/>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
@@ -5561,17 +5565,17 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>880000000106</t>
+          <t>880000000105</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>740066</t>
+          <t>740065</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>의료사회복지론</t>
+          <t>사회복지현장실무</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -5581,7 +5585,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>임성범</t>
+          <t>김소영</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5589,11 +5593,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M82" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M82" s="7"/>
     </row>
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
@@ -5623,22 +5623,22 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>880000000107</t>
+          <t>880000000106</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>740058</t>
+          <t>740066</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>발달심리</t>
+          <t>의료사회복지론</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>이계승</t>
+          <t>임성범</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -5656,7 +5656,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M83" s="7"/>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
@@ -5691,17 +5695,17 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>880000000108</t>
+          <t>880000000107</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>740059</t>
+          <t>740058</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>사회복지 전산실무Ⅱ</t>
+          <t>발달심리</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
@@ -5711,7 +5715,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>최은석</t>
+          <t>이계승</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5754,17 +5758,17 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>880000000109</t>
+          <t>880000000108</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>740060</t>
+          <t>740059</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>사회복지 현장실무Ⅱ</t>
+          <t>사회복지 전산실무Ⅱ</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -5774,7 +5778,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>변지호</t>
+          <t>최은석</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -5782,11 +5786,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M85" s="7"/>
     </row>
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>880000000110</t>
+          <t>880000000109</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>740061</t>
+          <t>740060</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>사회복지와 상담</t>
+          <t>사회복지 현장실무Ⅱ</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>김소영</t>
+          <t>변지호</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5849,7 +5849,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M86" s="7"/>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
@@ -5884,35 +5888,98 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
+          <t>880000000110</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>740061</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>사회복지와 상담</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>김소영</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>재직</t>
+        </is>
+      </c>
+      <c r="M87" s="7"/>
+    </row>
+    <row r="88" customHeight="true" ht="18.0">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>사회복지학과</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>학사학위 전공심화과정</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
           <t>880000000111</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>740062</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
         <is>
           <t>집단사회복지실천</t>
         </is>
       </c>
-      <c r="J87" s="4" t="inlineStr">
+      <c r="J88" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K87" s="4" t="inlineStr">
+      <c r="K88" s="4" t="inlineStr">
         <is>
           <t>조재삼</t>
         </is>
       </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>재직</t>
-        </is>
-      </c>
-      <c r="M87" s="7" t="inlineStr">
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>재직</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -2505,7 +2505,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M34" s="7"/>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
@@ -2568,7 +2572,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M35" s="7"/>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
@@ -4573,7 +4581,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M66" s="7"/>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -516,7 +516,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
@@ -1150,7 +1154,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -303,7 +303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.0" customWidth="true"/>
@@ -3230,7 +3230,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M45" s="7"/>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
@@ -4100,17 +4104,17 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>880000000080</t>
+          <t>880000000078</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>690057</t>
+          <t>690055</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>난독증진단평가</t>
+          <t>난독증기초</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -4120,7 +4124,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>하지명</t>
+          <t>김미진</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -4128,11 +4132,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M59" s="7"/>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>작업치료학과</t>
+          <t>언어치료학과</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>작업중심보조공학전문가과정(소단위_주문식)</t>
+          <t>난독재활치료전문가양성과정(소단위_주문식)</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -4167,27 +4167,27 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>880000000124</t>
+          <t>880000000079</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>700040</t>
+          <t>690056</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>운전재활,자동차보조공학</t>
+          <t>난독증중재</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>차선아</t>
+          <t>전은혜</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -4195,11 +4195,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M60" s="7"/>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
@@ -4219,12 +4215,12 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>작업치료학과</t>
+          <t>언어치료학과</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>작업중심보조공학전문가과정(소단위_주문식)</t>
+          <t>난독재활치료전문가양성과정(소단위_주문식)</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -4234,27 +4230,27 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>880000000125</t>
+          <t>880000000080</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>700042</t>
+          <t>690057</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>인간공학</t>
+          <t>난독증진단평가</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>강소라</t>
+          <t>하지명</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -4301,17 +4297,17 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>880000000126</t>
+          <t>880000000124</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>700043</t>
+          <t>700040</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>임상작업치료학특론</t>
+          <t>운전재활,자동차보조공학</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -4321,7 +4317,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>이정남</t>
+          <t>차선아</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -4368,17 +4364,17 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>880000000127</t>
+          <t>880000000125</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>700052</t>
+          <t>700042</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>장애학</t>
+          <t>인간공학</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -4388,7 +4384,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>김지훈</t>
+          <t>강소라</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -4420,12 +4416,12 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>뷰티코디네이션학과</t>
+          <t>작업치료학과</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>학사학위 전공심화과정</t>
+          <t>작업중심보조공학전문가과정(소단위_주문식)</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -4435,27 +4431,27 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>880000000059</t>
+          <t>880000000126</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>720001</t>
+          <t>700043</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>메디컬스킨케어실무</t>
+          <t>임상작업치료학특론</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>이지선</t>
+          <t>이정남</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4463,7 +4459,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M64" s="7"/>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>뷰티코디네이션학과</t>
+          <t>작업치료학과</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>학사학위 전공심화과정</t>
+          <t>작업중심보조공학전문가과정(소단위_주문식)</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>880000000060</t>
+          <t>880000000127</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>720002</t>
+          <t>700052</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>모발미용학</t>
+          <t>장애학</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>곽진만</t>
+          <t>김지훈</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -4526,7 +4526,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M65" s="7"/>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
@@ -4561,17 +4565,17 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>880000000061</t>
+          <t>880000000059</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>720003</t>
+          <t>720001</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>뷰티퍼스널컬러&amp;코디</t>
+          <t>메디컬스킨케어실무</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -4581,7 +4585,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>이현주</t>
+          <t>이지선</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4589,11 +4593,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M66" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M66" s="7"/>
     </row>
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>880000000062</t>
+          <t>880000000060</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>720004</t>
+          <t>720002</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>살롱두피&amp;헤드스파</t>
+          <t>모발미용학</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>박정은</t>
+          <t>곽진만</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>880000000063</t>
+          <t>880000000061</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>720005</t>
+          <t>720003</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>살롱미용영어</t>
+          <t>뷰티퍼스널컬러&amp;코디</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>이상록</t>
+          <t>이현주</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4719,7 +4719,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M68" s="7"/>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
@@ -4749,22 +4753,22 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>880000000064</t>
+          <t>880000000062</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>720011</t>
+          <t>720004</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>뷰티소셜미디어</t>
+          <t>살롱두피&amp;헤드스파</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -4774,7 +4778,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>황예지</t>
+          <t>박정은</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4782,11 +4786,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M69" s="7"/>
     </row>
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
@@ -4816,22 +4816,22 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>880000000065</t>
+          <t>880000000063</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>720012</t>
+          <t>720005</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>살롱업스타일</t>
+          <t>살롱미용영어</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>조미숙</t>
+          <t>이상록</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4849,11 +4849,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M70" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M70" s="7"/>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
@@ -4888,17 +4884,17 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>880000000066</t>
+          <t>880000000064</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>720013</t>
+          <t>720011</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>스폐셜테라피</t>
+          <t>뷰티소셜미디어</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4908,7 +4904,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>김명희</t>
+          <t>황예지</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4916,7 +4912,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M71" s="7"/>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>880000000067</t>
+          <t>880000000065</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>720014</t>
+          <t>720012</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>패션이미지메이크업&amp;스타일링</t>
+          <t>살롱업스타일</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>홍주연</t>
+          <t>조미숙</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4979,7 +4979,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M72" s="7"/>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
@@ -5014,17 +5018,17 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>880000000068</t>
+          <t>880000000066</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>720015</t>
+          <t>720013</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>화장품트렌드분석</t>
+          <t>스폐셜테라피</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -5034,7 +5038,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>김정은</t>
+          <t>김명희</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -5042,11 +5046,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M73" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M73" s="7"/>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>유아교육학과</t>
+          <t>뷰티코디네이션학과</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>880000000097</t>
+          <t>880000000067</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>731039</t>
+          <t>720014</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>가족상담</t>
+          <t>패션이미지메이크업&amp;스타일링</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>최인영</t>
+          <t>홍주연</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>유아교육학과</t>
+          <t>뷰티코디네이션학과</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -5139,32 +5139,32 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>880000000098</t>
+          <t>880000000068</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>731040</t>
+          <t>720015</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>장애영유아 통합교육</t>
+          <t>화장품트렌드분석</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>박정란</t>
+          <t>김정은</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -5172,7 +5172,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M75" s="7"/>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
@@ -5207,17 +5211,17 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>880000000099</t>
+          <t>880000000097</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>731041</t>
+          <t>731039</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>장애유아 진단 평가</t>
+          <t>가족상담</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -5227,7 +5231,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>김혜정</t>
+          <t>최인영</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -5270,17 +5274,17 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>880000000100</t>
+          <t>880000000098</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>731042</t>
+          <t>731040</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>특수교구 및 교재개발</t>
+          <t>장애영유아 통합교육</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -5290,7 +5294,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>김영훈</t>
+          <t>박정란</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -5318,7 +5322,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>사회복지학과</t>
+          <t>유아교육학과</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -5333,17 +5337,17 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>880000000101</t>
+          <t>880000000099</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>740037</t>
+          <t>731041</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>지역사회복지의 이해</t>
+          <t>장애유아 진단 평가</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -5353,7 +5357,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>조재삼</t>
+          <t>김혜정</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -5361,11 +5365,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M78" s="7"/>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>사회복지학과</t>
+          <t>유아교육학과</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -5400,17 +5400,17 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>880000000102</t>
+          <t>880000000100</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>740040</t>
+          <t>731042</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>사회복지실천의 이해</t>
+          <t>특수교구 및 교재개발</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>최은석</t>
+          <t>김영훈</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -5463,17 +5463,17 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>880000000103</t>
+          <t>880000000101</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>740042</t>
+          <t>740037</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>인간행동의 이해</t>
+          <t>지역사회복지의 이해</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>이재우</t>
+          <t>조재삼</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -5530,17 +5530,17 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>880000000104</t>
+          <t>880000000102</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>740063</t>
+          <t>740040</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>사회복지지도감독론</t>
+          <t>사회복지실천의 이해</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>강상훈</t>
+          <t>최은석</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -5558,11 +5558,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M81" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M81" s="7"/>
     </row>
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
@@ -5597,17 +5593,17 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>880000000105</t>
+          <t>880000000103</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>740065</t>
+          <t>740042</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>사회복지현장실무</t>
+          <t>인간행동의 이해</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -5617,7 +5613,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>김소영</t>
+          <t>이재우</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5664,17 +5660,17 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>880000000106</t>
+          <t>880000000104</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>740066</t>
+          <t>740063</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>의료사회복지론</t>
+          <t>사회복지지도감독론</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -5684,7 +5680,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>임성범</t>
+          <t>강상훈</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -5726,22 +5722,22 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>880000000107</t>
+          <t>880000000105</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>740058</t>
+          <t>740065</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>발달심리</t>
+          <t>사회복지현장실무</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
@@ -5751,7 +5747,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>이계승</t>
+          <t>김소영</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5759,7 +5755,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M84" s="7"/>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
@@ -5789,22 +5789,22 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>880000000108</t>
+          <t>880000000106</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>740059</t>
+          <t>740066</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>사회복지 전산실무Ⅱ</t>
+          <t>의료사회복지론</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>최은석</t>
+          <t>임성범</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -5822,7 +5822,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M85" s="7"/>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
@@ -5857,17 +5861,17 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>880000000109</t>
+          <t>880000000107</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>740060</t>
+          <t>740058</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>사회복지 현장실무Ⅱ</t>
+          <t>발달심리</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -5877,7 +5881,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>변지호</t>
+          <t>이계승</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5885,11 +5889,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M86" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M86" s="7"/>
     </row>
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
@@ -5924,17 +5924,17 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>880000000110</t>
+          <t>880000000108</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>740061</t>
+          <t>740059</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>사회복지와 상담</t>
+          <t>사회복지 전산실무Ⅱ</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>김소영</t>
+          <t>최은석</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -5952,11 +5952,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M87" s="7"/>
     </row>
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
@@ -5991,35 +5987,169 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
+          <t>880000000109</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>740060</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>사회복지 현장실무Ⅱ</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>변지호</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>재직</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" customHeight="true" ht="18.0">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>사회복지학과</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>학사학위 전공심화과정</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>880000000110</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>740061</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>사회복지와 상담</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>김소영</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>재직</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" customHeight="true" ht="18.0">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>사회복지학과</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>학사학위 전공심화과정</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
           <t>880000000111</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>740062</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
         <is>
           <t>집단사회복지실천</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="J90" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K88" s="4" t="inlineStr">
+      <c r="K90" s="4" t="inlineStr">
         <is>
           <t>조재삼</t>
         </is>
       </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>재직</t>
-        </is>
-      </c>
-      <c r="M88" s="7" t="inlineStr">
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>재직</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -4195,7 +4195,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M60" s="7"/>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -4790,7 +4790,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M69" s="7"/>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -965,7 +965,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -1028,7 +1032,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -2194,7 +2194,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M29" s="7"/>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
@@ -3557,7 +3561,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M50" s="7"/>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -2793,7 +2793,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M38" s="7"/>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
@@ -2856,7 +2860,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M39" s="7"/>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
@@ -2919,7 +2927,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M40" s="7"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
@@ -5070,7 +5082,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M73" s="7"/>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -3384,7 +3384,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M47" s="7"/>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -3061,7 +3061,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M42" s="7"/>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
@@ -3124,7 +3128,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M43" s="7"/>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -4109,7 +4109,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M58" s="7"/>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
@@ -4172,7 +4176,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M59" s="7"/>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -3786,7 +3786,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M53" s="7"/>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
@@ -4645,7 +4649,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M66" s="7"/>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
@@ -5425,7 +5433,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M78" s="7"/>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -1099,7 +1099,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -1690,7 +1694,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M21" s="7"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
@@ -1753,7 +1761,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M22" s="7"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -5500,7 +5512,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M79" s="7"/>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -4728,7 +4728,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M67" s="7"/>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -3932,7 +3932,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M55" s="7"/>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
@@ -4062,7 +4066,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M57" s="7"/>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -18,19 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="basefont"/>
-      <sz val="9.0"/>
-      <color rgb="002D3C51"/>
-      <u val="none"/>
     </font>
     <font>
       <name val="basefont"/>
@@ -270,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
@@ -289,9 +283,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -449,7 +440,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -516,7 +507,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -583,7 +574,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -650,7 +641,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M5" s="7"/>
+      <c r="M5" s="4"/>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
@@ -713,7 +704,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M6" s="7"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
@@ -776,7 +767,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M7" s="7"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -839,7 +830,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M8" s="7"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -902,7 +893,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -965,7 +956,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1032,7 +1023,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1099,7 +1090,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1166,7 +1157,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1233,7 +1224,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1300,7 +1291,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="4"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
@@ -1363,7 +1354,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1430,7 +1421,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M17" s="7"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
@@ -1493,7 +1488,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1560,7 +1555,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1627,7 +1622,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1694,7 +1689,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1761,7 +1756,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1828,7 +1823,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M23" s="7"/>
+      <c r="M23" s="4"/>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
@@ -1891,7 +1886,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M24" s="7"/>
+      <c r="M24" s="4"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
@@ -1954,7 +1949,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M25" s="7"/>
+      <c r="M25" s="4"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
@@ -2017,7 +2012,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M26" s="7"/>
+      <c r="M26" s="4"/>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
@@ -2080,7 +2075,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M27" s="7"/>
+      <c r="M27" s="4"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -2143,7 +2138,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M28" s="7"/>
+      <c r="M28" s="4"/>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
@@ -2206,7 +2201,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2273,7 +2268,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2340,7 +2335,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2407,7 +2402,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M32" s="7"/>
+      <c r="M32" s="4"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
@@ -2470,7 +2465,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2537,7 +2532,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2604,7 +2599,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2671,7 +2666,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2738,7 +2733,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2805,7 +2800,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr">
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2872,7 +2867,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2939,7 +2934,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3006,7 +3001,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3073,7 +3068,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3140,7 +3135,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3207,7 +3202,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M44" s="7" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3274,7 +3269,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3341,7 +3336,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M46" s="7"/>
+      <c r="M46" s="4"/>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
@@ -3404,7 +3399,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3471,7 +3466,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M48" s="7"/>
+      <c r="M48" s="4"/>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
@@ -3534,7 +3529,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M49" s="7"/>
+      <c r="M49" s="4"/>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
@@ -3597,7 +3592,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M50" s="7" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3664,7 +3659,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3731,7 +3726,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M52" s="7" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3798,7 +3793,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3865,7 +3860,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M54" s="7" t="inlineStr">
+      <c r="M54" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3932,7 +3927,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M55" s="7" t="inlineStr">
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -3999,7 +3994,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M56" s="7" t="inlineStr">
+      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4066,7 +4061,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M57" s="7" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4133,7 +4128,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M58" s="7" t="inlineStr">
+      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4200,7 +4195,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M59" s="7" t="inlineStr">
+      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4267,7 +4262,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M60" s="7" t="inlineStr">
+      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4334,7 +4329,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M61" s="7" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4401,7 +4396,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M62" s="7" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4468,7 +4463,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M63" s="7" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4535,7 +4530,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M64" s="7" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4602,7 +4597,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M65" s="7" t="inlineStr">
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4669,7 +4664,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M66" s="7" t="inlineStr">
+      <c r="M66" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4736,7 +4731,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M67" s="7" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4803,7 +4798,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M68" s="7" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4870,7 +4865,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr">
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -4937,7 +4932,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M70" s="7"/>
+      <c r="M70" s="4"/>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
@@ -5000,7 +4995,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M71" s="7" t="inlineStr">
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5067,7 +5062,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M72" s="7" t="inlineStr">
+      <c r="M72" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5134,7 +5129,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M73" s="7" t="inlineStr">
+      <c r="M73" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5201,7 +5196,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M74" s="7"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
@@ -5264,7 +5259,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M75" s="7" t="inlineStr">
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5331,7 +5326,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M76" s="7"/>
+      <c r="M76" s="4"/>
     </row>
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
@@ -5394,7 +5389,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M77" s="7"/>
+      <c r="M77" s="4"/>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
@@ -5457,7 +5452,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5524,7 +5519,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M79" s="7" t="inlineStr">
+      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5591,7 +5586,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M80" s="7" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5658,7 +5653,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M81" s="7"/>
+      <c r="M81" s="4"/>
     </row>
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
@@ -5721,7 +5716,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M82" s="7" t="inlineStr">
+      <c r="M82" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5788,7 +5783,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M83" s="7" t="inlineStr">
+      <c r="M83" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5855,7 +5850,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M84" s="7" t="inlineStr">
+      <c r="M84" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5922,7 +5917,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M85" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -5989,7 +5984,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M86" s="7"/>
+      <c r="M86" s="4"/>
     </row>
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
@@ -6052,7 +6047,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M87" s="7"/>
+      <c r="M87" s="4"/>
     </row>
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
@@ -6115,7 +6110,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M88" s="7" t="inlineStr">
+      <c r="M88" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -6182,7 +6177,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M89" s="7" t="inlineStr">
+      <c r="M89" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -6249,7 +6244,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M90" s="7" t="inlineStr">
+      <c r="M90" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -5196,7 +5196,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M74" s="4"/>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -5988,7 +5988,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M86" s="4"/>
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -2075,7 +2075,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M27" s="4"/>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -2138,7 +2142,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M28" s="4"/>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -641,7 +641,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M5" s="4"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
@@ -704,7 +708,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M6" s="4"/>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
@@ -767,7 +775,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M7" s="4"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -830,7 +842,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M8" s="4"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -5417,7 +5417,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M77" s="4"/>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -1965,7 +1965,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M25" s="4"/>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
@@ -2028,7 +2032,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M26" s="4"/>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
@@ -2426,7 +2434,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M32" s="4"/>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -5366,7 +5366,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M76" s="4"/>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -909,7 +909,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M9" s="4"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -1307,7 +1311,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M15" s="4"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -3573,7 +3573,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M49" s="4"/>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -1847,7 +1847,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M23" s="4"/>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
@@ -1910,7 +1914,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M24" s="4"/>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -3518,7 +3518,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M48" s="4"/>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -3388,7 +3388,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M46" s="4"/>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">

--- a/data_전공심화.xlsx
+++ b/data_전공심화.xlsx
@@ -4996,7 +4996,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M70" s="4"/>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
